--- a/Дело3а-78-2026Таганай/02_Отчёты/02.1_Обоснование_2024/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/02_Отчёты/02.1_Обоснование_2024/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.92537231826</v>
+        <v>46157.93110582924</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/02_Отчёты/02.1_Обоснование_2024/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/02_Отчёты/02.1_Обоснование_2024/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93110582924</v>
+        <v>46157.93365918886</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/02_Отчёты/02.1_Обоснование_2024/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/02_Отчёты/02.1_Обоснование_2024/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93365918886</v>
+        <v>46157.93668020055</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/02_Отчёты/02.1_Обоснование_2024/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/02_Отчёты/02.1_Обоснование_2024/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93668020055</v>
+        <v>46158.28192482626</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/02_Отчёты/02.1_Обоснование_2024/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/02_Отчёты/02.1_Обоснование_2024/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.28192482626</v>
+        <v>46158.29713612334</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/02_Отчёты/02.1_Обоснование_2024/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/02_Отчёты/02.1_Обоснование_2024/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.29713612334</v>
+        <v>46158.29787871755</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/02_Отчёты/02.1_Обоснование_2024/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/02_Отчёты/02.1_Обоснование_2024/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.29787871755</v>
+        <v>46158.33353949498</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/02_Отчёты/02.1_Обоснование_2024/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/02_Отчёты/02.1_Обоснование_2024/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.33353949498</v>
+        <v>46158.37209572274</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/02_Отчёты/02.1_Обоснование_2024/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/02_Отчёты/02.1_Обоснование_2024/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.37209572274</v>
+        <v>46158.37428740213</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">
